--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,7 +2712,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="n">
+      <c r="A163" s="2" t="n">
         <v>46269</v>
       </c>
       <c r="B163" t="n">
@@ -2723,6 +2723,20 @@
       </c>
       <c r="D163" t="n">
         <v>746</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B164" t="n">
+        <v>707</v>
+      </c>
+      <c r="C164" t="n">
+        <v>682</v>
+      </c>
+      <c r="D164" t="n">
+        <v>750</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2726,7 +2726,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="n">
+      <c r="A164" s="2" t="n">
         <v>46270</v>
       </c>
       <c r="B164" t="n">
@@ -2737,6 +2737,20 @@
       </c>
       <c r="D164" t="n">
         <v>750</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B165" t="n">
+        <v>714</v>
+      </c>
+      <c r="C165" t="n">
+        <v>687</v>
+      </c>
+      <c r="D165" t="n">
+        <v>753</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D165"/>
+  <dimension ref="A1:D166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2740,7 +2740,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="n">
+      <c r="A165" s="2" t="n">
         <v>46271</v>
       </c>
       <c r="B165" t="n">
@@ -2751,6 +2751,20 @@
       </c>
       <c r="D165" t="n">
         <v>753</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B166" t="n">
+        <v>718</v>
+      </c>
+      <c r="C166" t="n">
+        <v>691</v>
+      </c>
+      <c r="D166" t="n">
+        <v>756</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D166"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2754,7 +2754,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="n">
+      <c r="A166" s="2" t="n">
         <v>46272</v>
       </c>
       <c r="B166" t="n">
@@ -2765,6 +2765,20 @@
       </c>
       <c r="D166" t="n">
         <v>756</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B167" t="n">
+        <v>722</v>
+      </c>
+      <c r="C167" t="n">
+        <v>696</v>
+      </c>
+      <c r="D167" t="n">
+        <v>762</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D167"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2768,7 +2768,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="n">
+      <c r="A167" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="B167" t="n">
@@ -2779,6 +2779,20 @@
       </c>
       <c r="D167" t="n">
         <v>762</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B168" t="n">
+        <v>726</v>
+      </c>
+      <c r="C168" t="n">
+        <v>702</v>
+      </c>
+      <c r="D168" t="n">
+        <v>767</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D168"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2782,7 +2782,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n">
+      <c r="A168" s="2" t="n">
         <v>46274</v>
       </c>
       <c r="B168" t="n">
@@ -2793,6 +2793,20 @@
       </c>
       <c r="D168" t="n">
         <v>767</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B169" t="n">
+        <v>727</v>
+      </c>
+      <c r="C169" t="n">
+        <v>703</v>
+      </c>
+      <c r="D169" t="n">
+        <v>770</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2796,7 +2796,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="n">
+      <c r="A169" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="B169" t="n">
@@ -2807,6 +2807,20 @@
       </c>
       <c r="D169" t="n">
         <v>770</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B170" t="n">
+        <v>732</v>
+      </c>
+      <c r="C170" t="n">
+        <v>706</v>
+      </c>
+      <c r="D170" t="n">
+        <v>777</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2810,7 +2810,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="n">
+      <c r="A170" s="2" t="n">
         <v>46276</v>
       </c>
       <c r="B170" t="n">
@@ -2821,6 +2821,20 @@
       </c>
       <c r="D170" t="n">
         <v>777</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B171" t="n">
+        <v>738</v>
+      </c>
+      <c r="C171" t="n">
+        <v>708</v>
+      </c>
+      <c r="D171" t="n">
+        <v>784</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D171"/>
+  <dimension ref="A1:D172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2824,7 +2824,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="n">
+      <c r="A171" s="2" t="n">
         <v>46277</v>
       </c>
       <c r="B171" t="n">
@@ -2835,6 +2835,20 @@
       </c>
       <c r="D171" t="n">
         <v>784</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B172" t="n">
+        <v>743</v>
+      </c>
+      <c r="C172" t="n">
+        <v>713</v>
+      </c>
+      <c r="D172" t="n">
+        <v>789</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D172"/>
+  <dimension ref="A1:D173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2838,7 +2838,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n">
+      <c r="A172" s="2" t="n">
         <v>46278</v>
       </c>
       <c r="B172" t="n">
@@ -2849,6 +2849,20 @@
       </c>
       <c r="D172" t="n">
         <v>789</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B173" t="n">
+        <v>747</v>
+      </c>
+      <c r="C173" t="n">
+        <v>717</v>
+      </c>
+      <c r="D173" t="n">
+        <v>791</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D173"/>
+  <dimension ref="A1:D174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2852,7 +2852,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="n">
+      <c r="A173" s="2" t="n">
         <v>46279</v>
       </c>
       <c r="B173" t="n">
@@ -2863,6 +2863,20 @@
       </c>
       <c r="D173" t="n">
         <v>791</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B174" t="n">
+        <v>749</v>
+      </c>
+      <c r="C174" t="n">
+        <v>723</v>
+      </c>
+      <c r="D174" t="n">
+        <v>798</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D174"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2866,7 +2866,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="n">
+      <c r="A174" s="2" t="n">
         <v>46280</v>
       </c>
       <c r="B174" t="n">
@@ -2877,6 +2877,20 @@
       </c>
       <c r="D174" t="n">
         <v>798</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B175" t="n">
+        <v>756</v>
+      </c>
+      <c r="C175" t="n">
+        <v>727</v>
+      </c>
+      <c r="D175" t="n">
+        <v>802</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2880,7 +2880,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="n">
+      <c r="A175" s="2" t="n">
         <v>46281</v>
       </c>
       <c r="B175" t="n">
@@ -2891,6 +2891,20 @@
       </c>
       <c r="D175" t="n">
         <v>802</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B176" t="n">
+        <v>758</v>
+      </c>
+      <c r="C176" t="n">
+        <v>732</v>
+      </c>
+      <c r="D176" t="n">
+        <v>804</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D176"/>
+  <dimension ref="A1:D177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2894,7 +2894,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="n">
+      <c r="A176" s="2" t="n">
         <v>46282</v>
       </c>
       <c r="B176" t="n">
@@ -2905,6 +2905,20 @@
       </c>
       <c r="D176" t="n">
         <v>804</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B177" t="n">
+        <v>762</v>
+      </c>
+      <c r="C177" t="n">
+        <v>737</v>
+      </c>
+      <c r="D177" t="n">
+        <v>810</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D177"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2908,7 +2908,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="n">
+      <c r="A177" s="2" t="n">
         <v>46283</v>
       </c>
       <c r="B177" t="n">
@@ -2919,6 +2919,20 @@
       </c>
       <c r="D177" t="n">
         <v>810</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B178" t="n">
+        <v>764</v>
+      </c>
+      <c r="C178" t="n">
+        <v>743</v>
+      </c>
+      <c r="D178" t="n">
+        <v>817</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D178"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2922,7 +2922,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="n">
+      <c r="A178" s="2" t="n">
         <v>46284</v>
       </c>
       <c r="B178" t="n">
@@ -2933,6 +2933,20 @@
       </c>
       <c r="D178" t="n">
         <v>817</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B179" t="n">
+        <v>770</v>
+      </c>
+      <c r="C179" t="n">
+        <v>748</v>
+      </c>
+      <c r="D179" t="n">
+        <v>821</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D179"/>
+  <dimension ref="A1:D180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2936,7 +2936,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="n">
+      <c r="A179" s="2" t="n">
         <v>46285</v>
       </c>
       <c r="B179" t="n">
@@ -2946,6 +2946,20 @@
         <v>748</v>
       </c>
       <c r="D179" t="n">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B180" t="n">
+        <v>771</v>
+      </c>
+      <c r="C180" t="n">
+        <v>750</v>
+      </c>
+      <c r="D180" t="n">
         <v>821</v>
       </c>
     </row>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:D181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2950,7 +2950,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="n">
+      <c r="A180" s="2" t="n">
         <v>46286</v>
       </c>
       <c r="B180" t="n">
@@ -2961,6 +2961,20 @@
       </c>
       <c r="D180" t="n">
         <v>821</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B181" t="n">
+        <v>774</v>
+      </c>
+      <c r="C181" t="n">
+        <v>756</v>
+      </c>
+      <c r="D181" t="n">
+        <v>827</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2964,7 +2964,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="n">
+      <c r="A181" s="2" t="n">
         <v>46287</v>
       </c>
       <c r="B181" t="n">
@@ -2975,6 +2975,20 @@
       </c>
       <c r="D181" t="n">
         <v>827</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B182" t="n">
+        <v>784</v>
+      </c>
+      <c r="C182" t="n">
+        <v>756</v>
+      </c>
+      <c r="D182" t="n">
+        <v>833</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2978,7 +2978,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="n">
+      <c r="A182" s="2" t="n">
         <v>46288</v>
       </c>
       <c r="B182" t="n">
@@ -2989,6 +2989,20 @@
       </c>
       <c r="D182" t="n">
         <v>833</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B183" t="n">
+        <v>786</v>
+      </c>
+      <c r="C183" t="n">
+        <v>761</v>
+      </c>
+      <c r="D183" t="n">
+        <v>838</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D183"/>
+  <dimension ref="A1:D184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2992,7 +2992,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="n">
+      <c r="A183" s="2" t="n">
         <v>46289</v>
       </c>
       <c r="B183" t="n">
@@ -3003,6 +3003,20 @@
       </c>
       <c r="D183" t="n">
         <v>838</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B184" t="n">
+        <v>793</v>
+      </c>
+      <c r="C184" t="n">
+        <v>766</v>
+      </c>
+      <c r="D184" t="n">
+        <v>843</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D184"/>
+  <dimension ref="A1:D185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3006,7 +3006,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="n">
+      <c r="A184" s="2" t="n">
         <v>46290</v>
       </c>
       <c r="B184" t="n">
@@ -3017,6 +3017,20 @@
       </c>
       <c r="D184" t="n">
         <v>843</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B185" t="n">
+        <v>795</v>
+      </c>
+      <c r="C185" t="n">
+        <v>771</v>
+      </c>
+      <c r="D185" t="n">
+        <v>849</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D185"/>
+  <dimension ref="A1:D186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3020,7 +3020,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="n">
+      <c r="A185" s="2" t="n">
         <v>46291</v>
       </c>
       <c r="B185" t="n">
@@ -3031,6 +3031,20 @@
       </c>
       <c r="D185" t="n">
         <v>849</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B186" t="n">
+        <v>801</v>
+      </c>
+      <c r="C186" t="n">
+        <v>775</v>
+      </c>
+      <c r="D186" t="n">
+        <v>853</v>
       </c>
     </row>
   </sheetData>

--- a/Wins_Over_Time.xlsx
+++ b/Wins_Over_Time.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D186"/>
+  <dimension ref="A1:D187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3034,7 +3034,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="n">
+      <c r="A186" s="2" t="n">
         <v>46292</v>
       </c>
       <c r="B186" t="n">
@@ -3044,6 +3044,20 @@
         <v>775</v>
       </c>
       <c r="D186" t="n">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B187" t="n">
+        <v>801</v>
+      </c>
+      <c r="C187" t="n">
+        <v>775</v>
+      </c>
+      <c r="D187" t="n">
         <v>853</v>
       </c>
     </row>
